--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486814_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486814_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1492</v>
+        <v>8.1173</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8361</v>
+        <v>10.2015</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6869</v>
+        <v>-2.0842</v>
       </c>
       <c r="G2" t="n">
         <v>5.5835</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4732</v>
+        <v>1.4413</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8547</v>
+        <v>1.2201</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6185</v>
+        <v>0.2212</v>
       </c>
       <c r="V2" t="n">
         <v>0.8995</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.051</v>
+        <v>5.7532</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9983</v>
+        <v>7.3778</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9474</v>
+        <v>-1.6245</v>
       </c>
       <c r="G3" t="n">
         <v>4.1287</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2079</v>
+        <v>0.9102</v>
       </c>
       <c r="T3" t="n">
-        <v>1.627</v>
+        <v>1.0065</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4191</v>
+        <v>-0.0963</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6891</v>
+        <v>2.1182</v>
       </c>
       <c r="E4" t="n">
-        <v>3.956</v>
+        <v>3.3355</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2669</v>
+        <v>-1.2172</v>
       </c>
       <c r="G4" t="n">
         <v>1.7902</v>
@@ -766,13 +766,13 @@
         <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>0.833</v>
+        <v>0.2621</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2134</v>
+        <v>0.5929</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3805</v>
+        <v>-0.3308</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8995</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.868</v>
+        <v>1.4396</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4977</v>
+        <v>1.7629</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6297</v>
+        <v>-0.3233</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5496</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3794</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1702</v>
+        <v>0.1764</v>
       </c>
       <c r="J5" t="n">
-        <v>3.433</v>
+        <v>2.2733</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2763</v>
+        <v>1.6968</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1567</v>
+        <v>0.5766</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8833</v>
+        <v>-1.297</v>
       </c>
       <c r="N5" t="n">
         <v>-0.8969</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0135</v>
+        <v>-0.4002</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5461</v>
+        <v>0.3861</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3584</v>
+        <v>0.455</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1877</v>
+        <v>-0.0689</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8415</v>
+        <v>0.6565</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5133</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>1.1011</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1424</v>
+        <v>2.6563</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4474</v>
+        <v>-1.5552</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9762999999999999</v>
+        <v>2.5496</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.3794</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1764</v>
+        <v>2.1702</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2733</v>
+        <v>3.433</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6968</v>
+        <v>1.2763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5766</v>
+        <v>2.1567</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.297</v>
+        <v>-0.8833</v>
       </c>
       <c r="N6" t="n">
         <v>-0.8969</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4002</v>
+        <v>0.0135</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3586</v>
+        <v>0.7792</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1655</v>
+        <v>0.517</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.193</v>
+        <v>0.2622</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6565</v>
+        <v>-1.8415</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1505</v>
+        <v>0.8908</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7613</v>
+        <v>3.8989</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6108</v>
+        <v>-3.0081</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1367</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.292</v>
+        <v>0.4483</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6347</v>
+        <v>0.503</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3426</v>
+        <v>-0.0547</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0964</v>
+        <v>0.2743</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4194</v>
+        <v>0.5228</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.323</v>
+        <v>-0.2485</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1464</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1434</v>
+        <v>0.0345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7835</v>
+        <v>-0.2113</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8844</v>
+        <v>2.7857</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6679</v>
+        <v>-2.997</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2049</v>
+        <v>0.8784</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8342</v>
+        <v>-1.6558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3707</v>
+        <v>2.5343</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4321</v>
+        <v>4.0795</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0064</v>
+        <v>0.2069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5743</v>
+        <v>3.8726</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7728</v>
+        <v>-3.2011</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8278</v>
+        <v>-1.8628</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.945</v>
+        <v>-1.3384</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4214</v>
+        <v>0.2964</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3165</v>
+        <v>0.3513</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1049</v>
+        <v>-0.0549</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1754</v>
+        <v>-2.1006</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1168</v>
+        <v>0.2412</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2922</v>
+        <v>-2.3418</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4632</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3111</v>
+        <v>1.3858</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0681</v>
+        <v>1.1925</v>
       </c>
       <c r="U10" t="n">
-        <v>0.243</v>
+        <v>0.1934</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2469</v>
+        <v>-2.1245</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7997</v>
+        <v>0.1861</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0467</v>
+        <v>-2.3107</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8784</v>
+        <v>-0.5864</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6558</v>
+        <v>0.0896</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5343</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>4.0795</v>
+        <v>0.0207</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2069</v>
+        <v>0.0207</v>
       </c>
       <c r="L11" t="n">
-        <v>3.8726</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2011</v>
+        <v>-0.6071</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8628</v>
+        <v>0.0689</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3384</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7392</v>
+        <v>0.3034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6347</v>
+        <v>0.1654</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1045</v>
+        <v>0.138</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6138</v>
+        <v>-1.8415</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8995</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7605</v>
+        <v>-2.3845</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5998</v>
+        <v>-0.667</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3603</v>
+        <v>-1.7176</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5864</v>
+        <v>-3.2049</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0896</v>
+        <v>-2.8342</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.3707</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207</v>
+        <v>-1.4321</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0207</v>
+        <v>-2.0064</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.5743</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6071</v>
+        <v>-1.7728</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0689</v>
+        <v>-0.8278</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1390,22 +1390,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6674</v>
+        <v>0.8204</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.7651</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0883</v>
+        <v>0.0552</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4133</v>
+        <v>-4.2784</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.408</v>
+        <v>0.578</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.0054</v>
+        <v>-4.8564</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6781</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8937</v>
+        <v>0.2413</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6347</v>
+        <v>0.3513</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2591</v>
+        <v>-0.1101</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8415</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.319600000000001</v>
+        <v>8.595199999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>32.6039</v>
+        <v>32.87970000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-24.2846</v>
+        <v>-24.2845</v>
       </c>
       <c r="G14" t="n">
         <v>7.690999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.7933</v>
+        <v>-3.793299999999999</v>
       </c>
       <c r="I14" t="n">
         <v>11.4844</v>
@@ -1537,7 +1537,7 @@
         <v>-10.6935</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9652999999999998</v>
+        <v>-0.9653</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5848</v>
@@ -1546,13 +1546,13 @@
         <v>10.6194</v>
       </c>
       <c r="S14" t="n">
-        <v>7.033199999999999</v>
+        <v>7.309</v>
       </c>
       <c r="T14" t="n">
-        <v>6.892399999999999</v>
+        <v>7.1683</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1406000000000001</v>
+        <v>0.1406</v>
       </c>
       <c r="V14" t="n">
         <v>-5.4392</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6673</v>
+        <v>4.743</v>
       </c>
       <c r="E15" t="n">
-        <v>11.1269</v>
+        <v>11.4372</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.4596</v>
+        <v>-6.6942</v>
       </c>
       <c r="G15" t="n">
         <v>2.9353</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0203</v>
+        <v>-0.9446</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2763</v>
+        <v>0.034</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.744</v>
+        <v>-0.9786</v>
       </c>
       <c r="V15" t="n">
         <v>4.2969</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4327</v>
+        <v>1.1432</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8882</v>
+        <v>1.4745</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4554</v>
+        <v>-0.3313</v>
       </c>
       <c r="G16" t="n">
         <v>1.3776</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0551</v>
+        <v>-0.2344</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5239</v>
+        <v>0.1102</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4688</v>
+        <v>-0.3447</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7889</v>
+        <v>0.8074</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4903</v>
+        <v>1.9597</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2986</v>
+        <v>-1.1523</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4454</v>
+        <v>0.3729</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6761</v>
+        <v>-0.1313</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2306</v>
+        <v>0.5041</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3909</v>
+        <v>1.9806</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2281</v>
+        <v>-0.5446</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>2.5252</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9454</v>
+        <v>-1.6077</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5521</v>
+        <v>0.4134</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3934</v>
+        <v>-2.0211</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1158</v>
+        <v>-0.5308</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3584</v>
+        <v>-0.0208</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2426</v>
+        <v>-0.51</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4226</v>
+        <v>0.6525</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6495</v>
+        <v>0.18</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2268</v>
+        <v>0.4725</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3729</v>
+        <v>1.4454</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1313</v>
+        <v>1.6761</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5041</v>
+        <v>-0.2306</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9806</v>
+        <v>2.3909</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5446</v>
+        <v>2.2281</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5252</v>
+        <v>0.1628</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6077</v>
+        <v>-0.9454</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4134</v>
+        <v>-0.5521</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0211</v>
+        <v>-0.3934</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9654</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9156</v>
+        <v>-0.0207</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3311</v>
+        <v>0.0481</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5845</v>
+        <v>-0.0688</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2196</v>
+        <v>-0.3802</v>
       </c>
       <c r="E19" t="n">
-        <v>0.675</v>
+        <v>-0.049</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4554</v>
+        <v>-0.3313</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6078</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8273</v>
+        <v>0.2275</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1582</v>
+        <v>0.4343</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3309</v>
+        <v>-0.2068</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9274</v>
+        <v>-0.6253</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9133</v>
+        <v>1.0167</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8407</v>
+        <v>-1.6421</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0322</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8606</v>
+        <v>-0.5585</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3587</v>
+        <v>-0.2553</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5019</v>
+        <v>-0.3032</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0224</v>
+        <v>-1.5827</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4492</v>
+        <v>4.1731</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.4716</v>
+        <v>-5.7558</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6344</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3567</v>
+        <v>-0.917</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8002</v>
+        <v>-0.0762</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5565</v>
+        <v>-0.8408</v>
       </c>
       <c r="V21" t="n">
         <v>1.5133</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5681</v>
+        <v>-2.5666</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8623</v>
+        <v>2.552</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.4303</v>
+        <v>-5.1186</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3112</v>
@@ -2170,13 +2170,13 @@
         <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5738</v>
+        <v>-0.5724</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5512</v>
+        <v>0.241</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1251</v>
+        <v>-0.8133</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0013</v>
+        <v>-4.8997</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0316</v>
+        <v>0.7155</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.0329</v>
+        <v>-5.6152</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5836</v>
+        <v>-5.6532</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6756</v>
+        <v>-0.4966</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2591</v>
+        <v>-5.1566</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0525</v>
+        <v>1.2175</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5385</v>
+        <v>2.4698</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.486</v>
+        <v>-1.2523</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.6361</v>
+        <v>-6.8707</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8629</v>
+        <v>-2.9664</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.7731</v>
+        <v>-3.9043</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6108</v>
+        <v>-1.2619</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0555</v>
+        <v>-0.3935</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5553</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3313</v>
+        <v>-4.9213</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1984</v>
+        <v>0.8247</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5296</v>
+        <v>-5.746</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.6532</v>
+        <v>-3.5836</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4966</v>
+        <v>0.6756</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.1566</v>
+        <v>-4.2591</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2175</v>
+        <v>2.0525</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4698</v>
+        <v>2.5385</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2523</v>
+        <v>-0.486</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.8707</v>
+        <v>-5.6361</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.9664</v>
+        <v>-1.8629</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.9043</v>
+        <v>-3.7731</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6934</v>
+        <v>-1.5308</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9106</v>
+        <v>-0.2624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-1.2684</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.3194</v>
+        <v>-7.629699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>24.2847</v>
+        <v>24.2844</v>
       </c>
       <c r="F25" t="n">
-        <v>-32.6037</v>
+        <v>-31.9143</v>
       </c>
       <c r="G25" t="n">
         <v>-7.6912</v>
@@ -2404,13 +2404,13 @@
         <v>11.5847</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.032999999999999</v>
+        <v>-6.3436</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1407</v>
+        <v>-0.1406000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.8924</v>
+        <v>-6.203</v>
       </c>
       <c r="V25" t="n">
         <v>5.439299999999999</v>
